--- a/labs/day2/byod_anonymize_template.xlsx
+++ b/labs/day2/byod_anonymize_template.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>자사 엑셀 익명화(BYOD) 점검표 — 2일차 Standard · 6일차 기획서</t>
+          <t>자사 엑셀 익명화(BYOD) 점검표 — 2일차 다 했으면 · 6일차 기획서</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>원본은 내 PC의 엑셀 · Orange에서만 연다. 익명화본도 GitHub(개인 저장소 · fork)에는 올리지 않는다. AI에는 익명화본만, 학습 설정을 끈 뒤에 넣는다.</t>
+          <t>원본은 내 PC의 엑셀에서만 연다. 익명화본도 GitHub(개인 저장소 · fork)에는 올리지 않는다. AI에는 익명화본만, 학습 설정을 끈 뒤에 넣는다.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>쓰려는 AI 서비스의 학습 설정을 껐다(무료 소비자 AI · Colab AI에는 원본을 넣지 않는다)</t>
+          <t>쓰려는 AI 서비스의 학습 설정을 껐다(무료 소비자 AI에는 원본을 넣지 않는다)</t>
         </is>
       </c>
       <c r="F15" s="9" t="n"/>

--- a/labs/day2/byod_anonymize_template.xlsx
+++ b/labs/day2/byod_anonymize_template.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>자사 엑셀 익명화(BYOD) 점검표 — 2일차 다 했으면 · 6일차 기획서</t>
+          <t>자사 엑셀 익명화(BYOD) 점검표 — 내 업무 숫자를 다루기 전 · 6일차 기획서</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>원본은 내 PC의 엑셀에서만 연다. 익명화본도 GitHub(개인 저장소 · fork)에는 올리지 않는다. AI에는 익명화본만, 학습 설정을 끈 뒤에 넣는다.</t>
+          <t>원본은 내 PC의 엑셀에서만 연다. 익명화본도 GitHub(개인 저장소 · fork)와 과정의 AI 도구(ChatGPT · Claude · Claude Code)에는 넣지 않는다 — 내 PC의 엑셀 · 스크립트로만 다룬다(과정 뒤에는 회사가 허용한 AI 도구에서 같은 기준).</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>규칙은 과정 자료(데이터 조사 R08 §2.11)와 과정 사이트 '사전 준비 → 익명화 체크리스트'와 같다. 법률 자문이 아니다 — 회사 보안 규정 · NDA가 먼저다.</t>
+          <t>규칙은 과정 사이트 '사전 준비 → 익명화 체크리스트'와 같다. 법률 자문이 아니다 — 회사 보안 규정 · NDA가 먼저다.</t>
         </is>
       </c>
     </row>
